--- a/artfynd/A 12315-2024 artfynd.xlsx
+++ b/artfynd/A 12315-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,128 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124971749</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58016</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dusund, Dusund, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>724498</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6377532</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12315-2024 artfynd.xlsx
+++ b/artfynd/A 12315-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>124971749</v>
       </c>
       <c r="B4" t="n">
-        <v>58016</v>
+        <v>58134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 12315-2024 artfynd.xlsx
+++ b/artfynd/A 12315-2024 artfynd.xlsx
@@ -910,11 +910,6 @@
       <c r="B4" t="n">
         <v>58134</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 12315-2024 artfynd.xlsx
+++ b/artfynd/A 12315-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116674848</v>
+        <v>124971749</v>
       </c>
       <c r="B2" t="n">
-        <v>97690</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>102995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dusund, Dusund, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724574</v>
+        <v>724498</v>
       </c>
       <c r="R2" t="n">
-        <v>6377569</v>
+        <v>6377532</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,12 +760,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116674905</v>
+        <v>116674848</v>
       </c>
       <c r="B3" t="n">
-        <v>97796</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724498</v>
+        <v>724574</v>
       </c>
       <c r="R3" t="n">
-        <v>6377532</v>
+        <v>6377569</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,55 +902,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124971749</v>
+        <v>116674905</v>
       </c>
       <c r="B4" t="n">
-        <v>58134</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dusund, Dusund, Gtl</t>
@@ -990,12 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12315-2024 artfynd.xlsx
+++ b/artfynd/A 12315-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124971749</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116674848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116674905</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>